--- a/LearnerList.xlsx
+++ b/LearnerList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unextlearning-my.sharepoint.com/personal/vishal_chavan_u-next_com/Documents/AutoEmail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{94027174-82E9-414D-86F4-045F3AFD22DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88E3E17D-9703-474D-A628-F2846043F002}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{94027174-82E9-414D-86F4-045F3AFD22DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F88C8D7-7E33-4507-A434-BC3AB0432DA0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{31B92C47-5501-4F88-A2E6-0FC842132159}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>vishal@lms</t>
   </si>
@@ -66,15 +66,6 @@
   </si>
   <si>
     <t>vishal.chavan@u-next.com</t>
-  </si>
-  <si>
-    <t>Ashutosh</t>
-  </si>
-  <si>
-    <t>ashu@lms</t>
-  </si>
-  <si>
-    <t>ashutosh.yadav@u-next.com</t>
   </si>
   <si>
     <t>vishal1@lms</t>
@@ -146,9 +137,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}" name="Learner_List" displayName="Learner_List" ref="A1:E4" totalsRowShown="0" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:E4" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}" name="Learner_List" displayName="Learner_List" ref="A1:E3" totalsRowShown="0" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:E3" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E44A1F26-E9C4-4CB7-A304-41D654CF91DE}" name="SL No."/>
     <tableColumn id="2" xr3:uid="{B2067174-6DF5-4BB7-ACE0-16EA31EEA89F}" name="Name"/>
@@ -477,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE3263F-6F7F-4DBF-AA81-90AE0D15AD16}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -526,33 +521,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -560,16 +538,13 @@
     <hyperlink ref="E2" r:id="rId1" xr:uid="{0EB8579B-A027-4894-8F48-6DCB8FA4D619}"/>
     <hyperlink ref="C2" r:id="rId2" xr:uid="{EA877D6C-086C-4F52-B0DA-926D0299ABEB}"/>
     <hyperlink ref="D2" r:id="rId3" xr:uid="{6CD3FB63-1860-49B0-A2A7-450EA464A92F}"/>
-    <hyperlink ref="C3" r:id="rId4" xr:uid="{9ED65E6D-085C-4300-959C-3E8E74F8D013}"/>
-    <hyperlink ref="D3" r:id="rId5" xr:uid="{34F7F3E0-12F4-4FFF-9D5C-B9384F0134F6}"/>
-    <hyperlink ref="E3" r:id="rId6" xr:uid="{76193FBB-4BE1-40E7-AF29-A5437E19F4D5}"/>
-    <hyperlink ref="C4" r:id="rId7" xr:uid="{AD565F88-9B4C-4E80-94E3-53FF9E241BA9}"/>
-    <hyperlink ref="D4" r:id="rId8" xr:uid="{A9A4F2CA-3D42-4B92-A99C-B96500C1140E}"/>
-    <hyperlink ref="E4" r:id="rId9" xr:uid="{DCCEC9C7-BDC8-4E12-9E21-E118EC5E2418}"/>
+    <hyperlink ref="C3" r:id="rId4" xr:uid="{AD565F88-9B4C-4E80-94E3-53FF9E241BA9}"/>
+    <hyperlink ref="D3" r:id="rId5" xr:uid="{A9A4F2CA-3D42-4B92-A99C-B96500C1140E}"/>
+    <hyperlink ref="E3" r:id="rId6" xr:uid="{DCCEC9C7-BDC8-4E12-9E21-E118EC5E2418}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
--- a/LearnerList.xlsx
+++ b/LearnerList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unextlearning-my.sharepoint.com/personal/vishal_chavan_u-next_com/Documents/AutoEmail/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{94027174-82E9-414D-86F4-045F3AFD22DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F88C8D7-7E33-4507-A434-BC3AB0432DA0}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{94027174-82E9-414D-86F4-045F3AFD22DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9E91C87-8B74-4210-B746-AA48044F3ED6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{31B92C47-5501-4F88-A2E6-0FC842132159}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
-  <si>
-    <t>vishal@lms</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Name</t>
   </si>
@@ -72,6 +69,18 @@
   </si>
   <si>
     <t>vishalschavan4@gmail.com</t>
+  </si>
+  <si>
+    <t>vishal@yopmail.com</t>
+  </si>
+  <si>
+    <t>Test@123</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>corpsupport@u-next.com</t>
   </si>
 </sst>
 </file>
@@ -137,19 +146,16 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}" name="Learner_List" displayName="Learner_List" ref="A1:E3" totalsRowShown="0" dataCellStyle="Hyperlink">
-  <autoFilter ref="A1:E3" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}" name="Learner_List" displayName="Learner_List" ref="A1:F3" totalsRowShown="0" dataCellStyle="Hyperlink">
+  <autoFilter ref="A1:F3" xr:uid="{14C247B4-C3E0-4D61-A2E6-2F8A496CCD6F}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E44A1F26-E9C4-4CB7-A304-41D654CF91DE}" name="SL No."/>
     <tableColumn id="2" xr3:uid="{B2067174-6DF5-4BB7-ACE0-16EA31EEA89F}" name="Name"/>
     <tableColumn id="3" xr3:uid="{3E8814FC-93FE-428E-81F2-A7D63A116CA5}" name="username" dataCellStyle="Hyperlink"/>
     <tableColumn id="4" xr3:uid="{141CB974-C91E-4148-8E69-CBDA1467B723}" name="password" dataCellStyle="Hyperlink"/>
     <tableColumn id="5" xr3:uid="{49B08005-3578-43A6-9A6C-7AEC4A1128D9}" name="email" dataCellStyle="Hyperlink"/>
+    <tableColumn id="6" xr3:uid="{8F4795F3-316B-4F86-9EA3-810788A39520}" name="Support" dataCellStyle="Hyperlink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -472,7 +478,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE3263F-6F7F-4DBF-AA81-90AE0D15AD16}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -480,57 +486,67 @@
     <col min="3" max="3" width="17.26953125" customWidth="1"/>
     <col min="4" max="4" width="21.36328125" customWidth="1"/>
     <col min="5" max="5" width="27.81640625" customWidth="1"/>
+    <col min="6" max="6" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -541,10 +557,12 @@
     <hyperlink ref="C3" r:id="rId4" xr:uid="{AD565F88-9B4C-4E80-94E3-53FF9E241BA9}"/>
     <hyperlink ref="D3" r:id="rId5" xr:uid="{A9A4F2CA-3D42-4B92-A99C-B96500C1140E}"/>
     <hyperlink ref="E3" r:id="rId6" xr:uid="{DCCEC9C7-BDC8-4E12-9E21-E118EC5E2418}"/>
+    <hyperlink ref="F2" r:id="rId7" xr:uid="{55EF811F-F66A-40CE-B066-C05C3EFD5CF3}"/>
+    <hyperlink ref="F3" r:id="rId8" xr:uid="{4B7B5CF3-AA5B-4531-BD4F-B6ACADFB975B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId9"/>
   </tableParts>
 </worksheet>
 </file>